--- a/etf_holdings/2026-09-04_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-04_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -494,29 +494,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00407A(100,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00985A(-88,000)、00993A(-2,000)</t>
+          <t>00403A(-109,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -524,29 +524,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00993A(2,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00407A(-72,000)</t>
+          <t>00985A(-88,000)、00993A(-2,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -554,29 +554,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00993A(8,000)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00985A(-88,000)、00407A(-110,000)</t>
+          <t>00403A(-1,000,000)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>奇鋐科技</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -584,29 +584,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00993A(2,000)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>00985A(-24,000)、00993A(-2,000)</t>
+          <t>00407A(-72,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -614,29 +614,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>00993A(1,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00985A(-9,000)</t>
+          <t>00985A(-88,000)、00407A(-110,000)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -644,29 +644,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>00993A(11,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>00407A(-283,000)</t>
+          <t>00403A(-74,000)、00985A(-15,000)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>奇鋐科技</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -674,29 +674,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>00407A(37,000)、00993A(新納入)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00985A(-24,000)、00993A(-2,000)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>聯亞光電工業</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -709,24 +709,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>00981A(41,000)</t>
+          <t>00993A(1,000)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>00993A(-2,000)</t>
+          <t>00985A(-9,000)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -739,40 +739,130 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>00992A(200,000)</t>
+          <t>00993A(11,000)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>00993A(-6,000)</t>
+          <t>00407A(-283,000)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>00407A(37,000)、00993A(新納入)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>00981A(41,000)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>00993A(-2,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>00992A(200,000)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>00993A(-6,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>8996</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>高力熱處理工業</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>00993A(6,000)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>00985A(-37,000)</t>
         </is>

--- a/etf_holdings/2026-09-04_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-04_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -494,29 +494,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00407A(100,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00403A(-109,000)</t>
+          <t>00985A(-88,000)、00993A(-2,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -524,29 +524,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00993A(2,000)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00985A(-88,000)、00993A(-2,000)</t>
+          <t>00407A(-72,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -554,29 +554,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00993A(8,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00403A(-1,000,000)</t>
+          <t>00985A(-88,000)、00407A(-110,000)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>奇鋐科技</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -584,29 +584,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00993A(2,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>00407A(-72,000)</t>
+          <t>00985A(-24,000)、00993A(-2,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>聯亞光電工業</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -614,29 +614,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00993A(1,000)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00985A(-88,000)、00407A(-110,000)</t>
+          <t>00985A(-9,000)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -644,29 +644,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00993A(11,000)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>00403A(-74,000)、00985A(-15,000)</t>
+          <t>00407A(-283,000)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>奇鋐科技</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -674,29 +674,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>00407A(37,000)、00993A(新納入)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>00985A(-24,000)、00993A(-2,000)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -709,24 +709,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>00993A(1,000)</t>
+          <t>00981A(41,000)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>00985A(-9,000)</t>
+          <t>00993A(-2,000)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -739,24 +739,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>00993A(11,000)</t>
+          <t>00992A(200,000)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>00407A(-283,000)</t>
+          <t>00993A(-6,000)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>高力熱處理工業</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -764,105 +764,15 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>00407A(37,000)、00993A(新納入)</t>
+          <t>00993A(6,000)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>00981A(41,000)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>00993A(-2,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>00992A(200,000)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>00993A(-6,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>高力熱處理工業</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>00993A(6,000)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
         <is>
           <t>00985A(-37,000)</t>
         </is>
